--- a/admin/SciComp-Demos - Parts List - Sensors.xlsx
+++ b/admin/SciComp-Demos - Parts List - Sensors.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DaveB\Repos\scicomp-demos\admin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DaveB\SciComp\Courses\scicomp-demos\_archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388DCD20-1559-4BEF-A4AF-023519E484E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027AFAB6-06F5-457A-A9F1-FE57F9BCB9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{33F6F95C-2D53-4E62-A210-0FCD4640A9B8}"/>
   </bookViews>
@@ -278,7 +278,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -309,6 +309,12 @@
     <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -735,8 +741,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1B15000B-C80C-4FAD-949F-AB73D2A1A9B8}" name="Table4" displayName="Table4" ref="B63:H72" totalsRowCount="1" headerRowDxfId="10">
-  <autoFilter ref="B63:H71" xr:uid="{1B15000B-C80C-4FAD-949F-AB73D2A1A9B8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1B15000B-C80C-4FAD-949F-AB73D2A1A9B8}" name="Table4" displayName="Table4" ref="B64:H73" totalsRowCount="1" headerRowDxfId="10">
+  <autoFilter ref="B64:H72" xr:uid="{1B15000B-C80C-4FAD-949F-AB73D2A1A9B8}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{DAFCF0FF-D9BF-4CEF-834B-3406E64AD0D1}" name="Element ID" dataDxfId="9" totalsRowDxfId="8"/>
     <tableColumn id="2" xr3:uid="{73C9EAF7-C709-4AD0-AFC7-0D169ABA564F}" name="Design ID" dataDxfId="7" totalsRowDxfId="6"/>
@@ -745,7 +751,7 @@
     <tableColumn id="5" xr3:uid="{6C4FC6E9-D7B0-451F-AB3D-2BEE180A3DB1}" name="Qty" dataDxfId="5" totalsRowDxfId="4"/>
     <tableColumn id="6" xr3:uid="{7ED7C766-980B-4488-98FB-2D4156B57C18}" name="Unit Cost" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
     <tableColumn id="7" xr3:uid="{7D4587FC-F9C3-4F92-B73A-59C29101E5F1}" name="Total Cost" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Currency" totalsRowCellStyle="Currency">
-      <calculatedColumnFormula>+F64*G64</calculatedColumnFormula>
+      <calculatedColumnFormula>+F65*G65</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1049,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7AB3C2-C500-46AF-BB74-509C61346243}">
-  <dimension ref="B2:H75"/>
+  <dimension ref="B2:H76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="18.42578125" customWidth="1"/>
@@ -2026,274 +2032,278 @@
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="16" t="s">
         <v>43</v>
       </c>
+      <c r="D58" s="16"/>
       <c r="E58" s="13">
         <v>64.95</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="2" t="s">
+      <c r="C59" s="16" t="s">
         <v>44</v>
       </c>
+      <c r="D59" s="16"/>
       <c r="E59" s="13">
         <v>1.95</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C60" s="2" t="s">
+      <c r="C60" s="17" t="s">
         <v>45</v>
       </c>
+      <c r="D60" s="17"/>
       <c r="E60" s="13">
         <v>32.1</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C61" s="2" t="s">
+      <c r="C61" s="17" t="s">
         <v>46</v>
       </c>
+      <c r="D61" s="17"/>
       <c r="E61" s="13">
         <v>7.12</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="17" t="s">
         <v>47</v>
       </c>
+      <c r="D62" s="17"/>
       <c r="E62" s="13">
         <v>28.95</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+      <c r="E63" s="13"/>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
         <v>11</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>12</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D64" t="s">
         <v>1</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E64" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F64" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G64" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H64" s="7" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B64" s="1">
-        <v>300326</v>
-      </c>
-      <c r="C64" s="1">
-        <v>3003</v>
-      </c>
-      <c r="D64" t="s">
-        <v>48</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64" s="7">
-        <v>10</v>
-      </c>
-      <c r="G64" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H64" s="3">
-        <f>+F64*G64</f>
-        <v>1.4000000000000001</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B65" s="1">
-        <v>300226</v>
+        <v>300326</v>
       </c>
       <c r="C65" s="1">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="D65" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E65" t="s">
         <v>6</v>
       </c>
       <c r="F65" s="7">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G65" s="10">
-        <v>0.17</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H65" s="3">
-        <f t="shared" ref="H65:H71" si="1">+F65*G65</f>
-        <v>0.34</v>
+        <f>+F65*G65</f>
+        <v>1.4000000000000001</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B66" s="1">
-        <v>300926</v>
+        <v>300226</v>
       </c>
       <c r="C66" s="1">
-        <v>3009</v>
+        <v>3002</v>
       </c>
       <c r="D66" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E66" t="s">
         <v>6</v>
       </c>
       <c r="F66" s="7">
+        <v>2</v>
+      </c>
+      <c r="G66" s="10">
+        <v>0.17</v>
+      </c>
+      <c r="H66" s="3">
+        <f t="shared" ref="H66:H72" si="1">+F66*G66</f>
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="1">
+        <v>300926</v>
+      </c>
+      <c r="C67" s="1">
+        <v>3009</v>
+      </c>
+      <c r="D67" t="s">
+        <v>50</v>
+      </c>
+      <c r="E67" t="s">
+        <v>6</v>
+      </c>
+      <c r="F67" s="7">
         <v>3</v>
       </c>
-      <c r="G66" s="10">
+      <c r="G67" s="10">
         <v>0.25</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H67" s="3">
         <f t="shared" si="1"/>
         <v>0.75</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="1">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B68" s="1">
         <v>300426</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C68" s="1">
         <v>3004</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D68" t="s">
         <v>18</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E68" t="s">
         <v>6</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F68" s="7">
         <v>2</v>
       </c>
-      <c r="G67" s="10">
+      <c r="G68" s="10">
         <v>0.11</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H68" s="3">
         <f t="shared" si="1"/>
         <v>0.22</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="1">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B69" s="1">
         <v>303226</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C69" s="1">
         <v>3032</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D69" t="s">
         <v>26</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E69" t="s">
         <v>6</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F69" s="7">
         <v>1</v>
       </c>
-      <c r="G68" s="10">
+      <c r="G69" s="10">
         <v>0.43</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H69" s="3">
         <f t="shared" si="1"/>
         <v>0.43</v>
       </c>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="1">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B70" s="1">
         <v>303426</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C70" s="1">
         <v>3034</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D70" t="s">
         <v>35</v>
       </c>
-      <c r="E69" t="s">
+      <c r="E70" t="s">
         <v>6</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F70" s="7">
         <v>1</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G70" s="10">
         <v>0.25</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H70" s="3">
         <f t="shared" si="1"/>
         <v>0.25</v>
       </c>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="1">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B71" s="1">
         <v>303526</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C71" s="1">
         <v>3035</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D71" t="s">
         <v>51</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E71" t="s">
         <v>6</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F71" s="7">
         <v>1</v>
       </c>
-      <c r="G70" s="10">
+      <c r="G71" s="10">
         <v>0.46</v>
       </c>
-      <c r="H70" s="3">
+      <c r="H71" s="3">
         <f t="shared" si="1"/>
         <v>0.46</v>
       </c>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B71" s="1">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B72" s="1">
         <v>243121</v>
       </c>
-      <c r="C71" s="1">
+      <c r="C72" s="1">
         <v>2431</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D72" t="s">
         <v>52</v>
       </c>
-      <c r="E71" t="s">
+      <c r="E72" t="s">
         <v>17</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F72" s="7">
         <v>2</v>
       </c>
-      <c r="G71" s="10">
+      <c r="G72" s="10">
         <v>0.13</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H72" s="3">
         <f t="shared" si="1"/>
         <v>0.26</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="G72" s="10"/>
-      <c r="H72" s="15">
-        <f>SUBTOTAL(109,Table4[Total Cost])</f>
-        <v>4.1100000000000003</v>
       </c>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
       <c r="G73" s="10"/>
-      <c r="H73" s="3"/>
+      <c r="H73" s="15">
+        <f>SUBTOTAL(109,Table4[Total Cost])</f>
+        <v>4.1100000000000003</v>
+      </c>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B74" s="1"/>
@@ -2307,7 +2317,20 @@
       <c r="G75" s="10"/>
       <c r="H75" s="3"/>
     </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="G76" s="10"/>
+      <c r="H76" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C58:D58"/>
+    <mergeCell ref="C59:D59"/>
+    <mergeCell ref="C60:D60"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+  </mergeCells>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{17EF0979-152B-4972-9745-8AAEE713699A}"/>
     <hyperlink ref="C9" r:id="rId2" xr:uid="{8ED3F0F8-EBFB-43AC-8BD0-C2BAE22CF7E4}"/>

--- a/admin/SciComp-Demos - Parts List - Sensors.xlsx
+++ b/admin/SciComp-Demos - Parts List - Sensors.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DaveB\SciComp\Courses\scicomp-demos\_archive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DaveB\Repos\scicomp-demos\admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027AFAB6-06F5-457A-A9F1-FE57F9BCB9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EE21EA-0340-4216-91E0-E0FFB7BD3EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{33F6F95C-2D53-4E62-A210-0FCD4640A9B8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{33F6F95C-2D53-4E62-A210-0FCD4640A9B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="64">
   <si>
     <t>PLATE, 6x10</t>
   </si>
@@ -180,21 +180,6 @@
     <t>4 in x 30 ft - Vibrancy Enhancing Projector Felt Tape</t>
   </si>
   <si>
-    <t>BRICK 2X2</t>
-  </si>
-  <si>
-    <t>BRICK 2X3</t>
-  </si>
-  <si>
-    <t>BRICK 1X6</t>
-  </si>
-  <si>
-    <t>PLATE 4X8</t>
-  </si>
-  <si>
-    <t>FLAT TILE 1X4</t>
-  </si>
-  <si>
     <t>Uranium Ore</t>
   </si>
   <si>
@@ -214,6 +199,33 @@
   </si>
   <si>
     <t>Geiger Counter Lab</t>
+  </si>
+  <si>
+    <t>Brick 2x2</t>
+  </si>
+  <si>
+    <t>Plate 1x1</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Plate 1x2</t>
+  </si>
+  <si>
+    <t>Plate 1x4</t>
+  </si>
+  <si>
+    <t>Plate 1x6</t>
+  </si>
+  <si>
+    <t>Plate 1x8</t>
+  </si>
+  <si>
+    <t>Plate 2x3</t>
+  </si>
+  <si>
+    <t>Plate 2x4</t>
   </si>
 </sst>
 </file>
@@ -224,7 +236,7 @@
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -255,6 +267,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -278,7 +296,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -308,12 +326,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="8" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -339,6 +353,20 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -378,35 +406,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -741,17 +741,17 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1B15000B-C80C-4FAD-949F-AB73D2A1A9B8}" name="Table4" displayName="Table4" ref="B64:H73" totalsRowCount="1" headerRowDxfId="10">
-  <autoFilter ref="B64:H72" xr:uid="{1B15000B-C80C-4FAD-949F-AB73D2A1A9B8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{ED86F80A-9490-47C4-A2FF-67B35D5F0FE5}" name="Table4" displayName="Table4" ref="B63:H72" totalsRowCount="1" headerRowDxfId="10">
+  <autoFilter ref="B63:H71" xr:uid="{ED86F80A-9490-47C4-A2FF-67B35D5F0FE5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{DAFCF0FF-D9BF-4CEF-834B-3406E64AD0D1}" name="Element ID" dataDxfId="9" totalsRowDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{73C9EAF7-C709-4AD0-AFC7-0D169ABA564F}" name="Design ID" dataDxfId="7" totalsRowDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{F6DD72BB-F286-4FDA-BDEF-67639D93CFC4}" name="Description"/>
-    <tableColumn id="4" xr3:uid="{8DB7E819-EA02-4F03-843C-FDAA6A0583FD}" name="Color"/>
-    <tableColumn id="5" xr3:uid="{6C4FC6E9-D7B0-451F-AB3D-2BEE180A3DB1}" name="Qty" dataDxfId="5" totalsRowDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{7ED7C766-980B-4488-98FB-2D4156B57C18}" name="Unit Cost" dataDxfId="3" totalsRowDxfId="2" dataCellStyle="Currency" totalsRowCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{7D4587FC-F9C3-4F92-B73A-59C29101E5F1}" name="Total Cost" totalsRowFunction="sum" dataDxfId="1" totalsRowDxfId="0" dataCellStyle="Currency" totalsRowCellStyle="Currency">
-      <calculatedColumnFormula>+F65*G65</calculatedColumnFormula>
+    <tableColumn id="1" xr3:uid="{76683875-8A56-4F53-859B-C02B19E915BF}" name="Element ID" dataDxfId="9" totalsRowDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{ECBF4B54-158C-4E13-990C-952F3373DDE9}" name="Design ID" dataDxfId="8" totalsRowDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{8E84BCA3-B96C-4CC1-AF13-26EDB9167C07}" name="Description"/>
+    <tableColumn id="4" xr3:uid="{C862CDFC-D73B-4F47-94A4-E1D7370379A5}" name="Color"/>
+    <tableColumn id="5" xr3:uid="{B43D0DCD-ECEA-406C-8A5B-D2BF6B6910C7}" name="Qty" dataDxfId="7" totalsRowDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{8128B79B-0831-40FD-80AD-20E6141C8423}" name="Unit Cost" dataDxfId="6" totalsRowDxfId="1" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{14815AF1-48E9-4861-A340-D74D8373666B}" name="Total Cost" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="0" dataCellStyle="Currency">
+      <calculatedColumnFormula>+F64*G64</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1055,7 +1055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7AB3C2-C500-46AF-BB74-509C61346243}">
-  <dimension ref="B2:H76"/>
+  <dimension ref="B2:H72"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="18.42578125" customWidth="1"/>
@@ -1068,7 +1068,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -1078,7 +1078,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
@@ -1091,7 +1091,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C7" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E7" s="13">
         <v>39.950000000000003</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
@@ -1397,7 +1397,7 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
@@ -1679,7 +1679,7 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
@@ -2028,320 +2028,254 @@
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C58" s="16" t="s">
+      <c r="C58" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D58" s="16"/>
       <c r="E58" s="13">
         <v>64.95</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C59" s="16" t="s">
+      <c r="C59" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D59" s="16"/>
       <c r="E59" s="13">
         <v>1.95</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D60" s="17"/>
       <c r="E60" s="13">
         <v>32.1</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C61" s="17" t="s">
+      <c r="C61" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D61" s="17"/>
       <c r="E61" s="13">
         <v>7.12</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D62" s="17"/>
       <c r="E62" s="13">
         <v>28.95</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="13"/>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>12</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1</v>
+      </c>
+      <c r="E63" t="s">
+        <v>5</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B64" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" t="s">
+        <v>55</v>
+      </c>
+      <c r="E64" t="s">
+        <v>6</v>
+      </c>
+      <c r="F64">
         <v>12</v>
       </c>
-      <c r="D64" t="s">
+      <c r="G64" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="H64" s="3">
+        <f>+F64*G64</f>
+        <v>1.6800000000000002</v>
+      </c>
+    </row>
+    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" t="s">
+        <v>56</v>
+      </c>
+      <c r="E65" t="s">
+        <v>57</v>
+      </c>
+      <c r="F65">
+        <v>3</v>
+      </c>
+      <c r="G65" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="H65" s="3">
+        <f t="shared" ref="H65:H70" si="1">+F65*G65</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" t="s">
+        <v>57</v>
+      </c>
+      <c r="F66">
+        <v>2</v>
+      </c>
+      <c r="G66" s="10">
+        <v>0.161</v>
+      </c>
+      <c r="H66" s="3">
+        <f t="shared" si="1"/>
+        <v>0.32200000000000001</v>
+      </c>
+    </row>
+    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" t="s">
+        <v>59</v>
+      </c>
+      <c r="E67" t="s">
+        <v>57</v>
+      </c>
+      <c r="F67">
         <v>1</v>
       </c>
-      <c r="E64" t="s">
-        <v>5</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B65" s="1">
-        <v>300326</v>
-      </c>
-      <c r="C65" s="1">
-        <v>3003</v>
-      </c>
-      <c r="D65" t="s">
-        <v>48</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" s="7">
-        <v>10</v>
-      </c>
-      <c r="G65" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H65" s="3">
-        <f>+F65*G65</f>
-        <v>1.4000000000000001</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B66" s="1">
-        <v>300226</v>
-      </c>
-      <c r="C66" s="1">
-        <v>3002</v>
-      </c>
-      <c r="D66" t="s">
-        <v>49</v>
-      </c>
-      <c r="E66" t="s">
-        <v>6</v>
-      </c>
-      <c r="F66" s="7">
-        <v>2</v>
-      </c>
-      <c r="G66" s="10">
-        <v>0.17</v>
-      </c>
-      <c r="H66" s="3">
-        <f t="shared" ref="H66:H72" si="1">+F66*G66</f>
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B67" s="1">
-        <v>300926</v>
-      </c>
-      <c r="C67" s="1">
-        <v>3009</v>
-      </c>
-      <c r="D67" t="s">
-        <v>50</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" s="7">
-        <v>3</v>
-      </c>
       <c r="G67" s="10">
-        <v>0.25</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="H67" s="3">
         <f t="shared" si="1"/>
-        <v>0.75</v>
+        <v>0.26500000000000001</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B68" s="1">
-        <v>300426</v>
-      </c>
-      <c r="C68" s="1">
-        <v>3004</v>
-      </c>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
       <c r="D68" t="s">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="E68" t="s">
-        <v>6</v>
-      </c>
-      <c r="F68" s="7">
-        <v>2</v>
+        <v>57</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
       </c>
       <c r="G68" s="10">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H68" s="3">
         <f t="shared" si="1"/>
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B69" s="1">
-        <v>303226</v>
-      </c>
-      <c r="C69" s="1">
-        <v>3032</v>
-      </c>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" s="7">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="F69">
+        <v>2</v>
       </c>
       <c r="G69" s="10">
-        <v>0.43</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="H69" s="3">
         <f t="shared" si="1"/>
-        <v>0.43</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B70" s="1">
-        <v>303426</v>
-      </c>
-      <c r="C70" s="1">
-        <v>3034</v>
-      </c>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
       <c r="D70" t="s">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="E70" t="s">
-        <v>6</v>
-      </c>
-      <c r="F70" s="7">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="F70">
+        <v>4</v>
       </c>
       <c r="G70" s="10">
-        <v>0.25</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H70" s="3">
         <f t="shared" si="1"/>
-        <v>0.25</v>
+        <v>1.1200000000000001</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B71" s="1">
-        <v>303526</v>
-      </c>
-      <c r="C71" s="1">
-        <v>3035</v>
-      </c>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
       <c r="D71" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" s="7">
-        <v>1</v>
+        <v>57</v>
+      </c>
+      <c r="F71">
+        <v>4</v>
       </c>
       <c r="G71" s="10">
-        <v>0.46</v>
+        <v>0.214</v>
       </c>
       <c r="H71" s="3">
-        <f t="shared" si="1"/>
-        <v>0.46</v>
+        <f>+F71*G71</f>
+        <v>0.85599999999999998</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B72" s="1">
-        <v>243121</v>
-      </c>
-      <c r="C72" s="1">
-        <v>2431</v>
-      </c>
-      <c r="D72" t="s">
-        <v>52</v>
-      </c>
-      <c r="E72" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72" s="7">
-        <v>2</v>
-      </c>
-      <c r="G72" s="10">
-        <v>0.13</v>
-      </c>
-      <c r="H72" s="3">
-        <f t="shared" si="1"/>
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="G73" s="10"/>
-      <c r="H73" s="15">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="G72" s="15"/>
+      <c r="H72" s="14">
         <f>SUBTOTAL(109,Table4[Total Cost])</f>
-        <v>4.1100000000000003</v>
-      </c>
-    </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="G74" s="10"/>
-      <c r="H74" s="3"/>
-    </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="G75" s="10"/>
-      <c r="H75" s="3"/>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="G76" s="10"/>
-      <c r="H76" s="3"/>
+        <v>6.1630000000000003</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="C58:D58"/>
-    <mergeCell ref="C59:D59"/>
-    <mergeCell ref="C60:D60"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-  </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="C3" r:id="rId1" xr:uid="{17EF0979-152B-4972-9745-8AAEE713699A}"/>
     <hyperlink ref="C9" r:id="rId2" xr:uid="{8ED3F0F8-EBFB-43AC-8BD0-C2BAE22CF7E4}"/>
     <hyperlink ref="C6" r:id="rId3" xr:uid="{43E2B375-B2A3-431F-9CCD-C2F5B2832378}"/>
     <hyperlink ref="C8" r:id="rId4" xr:uid="{8AFB8533-6E4E-46B4-B8D9-FFFE940BAA89}"/>
-    <hyperlink ref="C58" r:id="rId5" xr:uid="{50B5993D-BB00-48A4-809D-EA5CA7349311}"/>
-    <hyperlink ref="C59" r:id="rId6" xr:uid="{6D8BC74E-B55C-461E-AE65-10221A386BEA}"/>
-    <hyperlink ref="C60" r:id="rId7" xr:uid="{83A5B3C8-9351-4C2A-ADFA-3FFC74A6D915}"/>
-    <hyperlink ref="C61" r:id="rId8" xr:uid="{FF3E4C1D-95D1-427F-A4E9-943E7C0B0497}"/>
-    <hyperlink ref="C62" r:id="rId9" xr:uid="{0CF55A9C-8080-42EF-8430-343E3E3525B2}"/>
-    <hyperlink ref="C7" r:id="rId10" display="Images SI - Uranium Ore" xr:uid="{2A42E8E4-BEF6-4EA2-A0A4-DCE432363EC4}"/>
+    <hyperlink ref="C7" r:id="rId5" display="Images SI - Uranium Ore" xr:uid="{2A42E8E4-BEF6-4EA2-A0A4-DCE432363EC4}"/>
+    <hyperlink ref="C58" r:id="rId6" xr:uid="{DFB97EF8-2D11-41EA-93D2-F9D44BB1F7E8}"/>
+    <hyperlink ref="C59" r:id="rId7" xr:uid="{B558DB4E-2986-4C97-860B-41251108BACC}"/>
+    <hyperlink ref="C60" r:id="rId8" xr:uid="{CED55952-7AA0-43D2-AA98-56F5292C2EAC}"/>
+    <hyperlink ref="C61" r:id="rId9" xr:uid="{34EEC311-38EF-4430-9526-0F77F964AECA}"/>
+    <hyperlink ref="C62" r:id="rId10" xr:uid="{F6A0BDC3-0ED2-48CA-9FF7-7CC73CA1EA9E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId11"/>

--- a/admin/SciComp-Demos - Parts List - Sensors.xlsx
+++ b/admin/SciComp-Demos - Parts List - Sensors.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DaveB\Repos\scicomp-demos\admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EE21EA-0340-4216-91E0-E0FFB7BD3EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E38FEC5-7A8E-40D5-B8F1-A77E3964FC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{33F6F95C-2D53-4E62-A210-0FCD4640A9B8}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="67">
   <si>
     <t>PLATE, 6x10</t>
   </si>
@@ -168,9 +168,6 @@
     <t>SparkFun Triad Spectroscopy Sensor - AS7265x (Qwiic)</t>
   </si>
   <si>
-    <t>SparkFun Qwiic Cable - 500mm</t>
-  </si>
-  <si>
     <t>Specimen Density Set (Ten Cube)</t>
   </si>
   <si>
@@ -226,6 +223,18 @@
   </si>
   <si>
     <t>Plate 2x4</t>
+  </si>
+  <si>
+    <t>Plate 2x8</t>
+  </si>
+  <si>
+    <t>Brick Link Lego Part Order Online</t>
+  </si>
+  <si>
+    <t>SparkFun Serial Basic Breakout - CH340C and USB-C</t>
+  </si>
+  <si>
+    <t>8 more</t>
   </si>
 </sst>
 </file>
@@ -296,7 +305,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -329,6 +338,9 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -336,6 +348,24 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="43">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -356,37 +386,6 @@
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <b val="0"/>
         <i val="0"/>
@@ -406,7 +405,20 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -741,17 +753,17 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{ED86F80A-9490-47C4-A2FF-67B35D5F0FE5}" name="Table4" displayName="Table4" ref="B63:H72" totalsRowCount="1" headerRowDxfId="10">
-  <autoFilter ref="B63:H71" xr:uid="{ED86F80A-9490-47C4-A2FF-67B35D5F0FE5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{ED86F80A-9490-47C4-A2FF-67B35D5F0FE5}" name="Table4" displayName="Table4" ref="B64:H74" totalsRowCount="1" headerRowDxfId="10">
+  <autoFilter ref="B64:H73" xr:uid="{ED86F80A-9490-47C4-A2FF-67B35D5F0FE5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{76683875-8A56-4F53-859B-C02B19E915BF}" name="Element ID" dataDxfId="9" totalsRowDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{ECBF4B54-158C-4E13-990C-952F3373DDE9}" name="Design ID" dataDxfId="8" totalsRowDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{76683875-8A56-4F53-859B-C02B19E915BF}" name="Element ID" dataDxfId="8" totalsRowDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{ECBF4B54-158C-4E13-990C-952F3373DDE9}" name="Design ID" dataDxfId="6" totalsRowDxfId="7"/>
     <tableColumn id="3" xr3:uid="{8E84BCA3-B96C-4CC1-AF13-26EDB9167C07}" name="Description"/>
     <tableColumn id="4" xr3:uid="{C862CDFC-D73B-4F47-94A4-E1D7370379A5}" name="Color"/>
-    <tableColumn id="5" xr3:uid="{B43D0DCD-ECEA-406C-8A5B-D2BF6B6910C7}" name="Qty" dataDxfId="7" totalsRowDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{8128B79B-0831-40FD-80AD-20E6141C8423}" name="Unit Cost" dataDxfId="6" totalsRowDxfId="1" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{14815AF1-48E9-4861-A340-D74D8373666B}" name="Total Cost" totalsRowFunction="sum" dataDxfId="5" totalsRowDxfId="0" dataCellStyle="Currency">
-      <calculatedColumnFormula>+F64*G64</calculatedColumnFormula>
+    <tableColumn id="5" xr3:uid="{B43D0DCD-ECEA-406C-8A5B-D2BF6B6910C7}" name="Qty" dataDxfId="4" totalsRowDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{8128B79B-0831-40FD-80AD-20E6141C8423}" name="Unit Cost" dataDxfId="2" totalsRowDxfId="3" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{14815AF1-48E9-4861-A340-D74D8373666B}" name="Total Cost" totalsRowFunction="sum" dataDxfId="0" totalsRowDxfId="1" dataCellStyle="Currency">
+      <calculatedColumnFormula>+F65*G65</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1055,7 +1067,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED7AB3C2-C500-46AF-BB74-509C61346243}">
-  <dimension ref="B2:H72"/>
+  <dimension ref="B2:I74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="18.42578125" customWidth="1"/>
@@ -1068,7 +1080,7 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
@@ -1078,7 +1090,7 @@
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
@@ -1091,7 +1103,7 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C7" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" s="13">
         <v>39.950000000000003</v>
@@ -1115,7 +1127,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
@@ -1397,7 +1409,7 @@
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
@@ -1679,7 +1691,7 @@
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
@@ -2028,7 +2040,7 @@
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B57" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.25">
@@ -2041,15 +2053,15 @@
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C59" s="2" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="E59" s="13">
-        <v>1.95</v>
+        <v>9.9499999999999993</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C60" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E60" s="13">
         <v>32.1</v>
@@ -2057,7 +2069,7 @@
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C61" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E61" s="13">
         <v>7.12</v>
@@ -2065,202 +2077,262 @@
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.25">
       <c r="C62" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E62" s="13">
         <v>28.95</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B63" t="s">
+      <c r="C63" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
         <v>11</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>12</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D64" t="s">
         <v>1</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E64" t="s">
         <v>5</v>
       </c>
-      <c r="F63" s="7" t="s">
+      <c r="F64" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G63" s="7" t="s">
+      <c r="G64" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H63" s="7" t="s">
+      <c r="H64" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" t="s">
-        <v>55</v>
-      </c>
-      <c r="E64" t="s">
-        <v>6</v>
-      </c>
-      <c r="F64">
-        <v>12</v>
-      </c>
-      <c r="G64" s="10">
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="H64" s="3">
-        <f>+F64*G64</f>
-        <v>1.6800000000000002</v>
-      </c>
-    </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>6</v>
       </c>
       <c r="F65">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G65" s="10">
-        <v>0.25</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="H65" s="3">
-        <f t="shared" ref="H65:H70" si="1">+F65*G65</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+        <f>+F65*G65</f>
+        <v>1.6800000000000002</v>
+      </c>
+      <c r="I65" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G66" s="10">
-        <v>0.161</v>
+        <v>0.25</v>
       </c>
       <c r="H66" s="3">
-        <f t="shared" si="1"/>
-        <v>0.32200000000000001</v>
-      </c>
-    </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" ref="H66:H71" si="1">+F66*G66</f>
+        <v>1</v>
+      </c>
+      <c r="I66">
+        <f>+Table4[[#This Row],[Qty]]*8</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
       <c r="D67" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E67" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F67">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G67" s="10">
-        <v>0.26500000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="H67" s="3">
         <f t="shared" si="1"/>
-        <v>0.26500000000000001</v>
-      </c>
-    </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.32200000000000001</v>
+      </c>
+      <c r="I67">
+        <f>+Table4[[#This Row],[Qty]]*8</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="D68" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F68">
         <v>1</v>
       </c>
       <c r="G68" s="10">
-        <v>0.26</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="H68" s="3">
         <f t="shared" si="1"/>
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="I68">
+        <f>+Table4[[#This Row],[Qty]]*8</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
       <c r="D69" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E69" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G69" s="10">
-        <v>0.45500000000000002</v>
+        <v>0.26</v>
       </c>
       <c r="H69" s="3">
         <f t="shared" si="1"/>
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+        <v>0.78</v>
+      </c>
+      <c r="I69">
+        <f>+Table4[[#This Row],[Qty]]*8</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
       <c r="D70" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F70">
         <v>4</v>
       </c>
       <c r="G70" s="10">
-        <v>0.28000000000000003</v>
+        <v>0.45500000000000002</v>
       </c>
       <c r="H70" s="3">
         <f t="shared" si="1"/>
-        <v>1.1200000000000001</v>
-      </c>
-    </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+        <v>1.82</v>
+      </c>
+      <c r="I70">
+        <f>+Table4[[#This Row],[Qty]]*8</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
       <c r="D71" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G71" s="10">
-        <v>0.214</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="H71" s="3">
-        <f>+F71*G71</f>
-        <v>0.85599999999999998</v>
-      </c>
-    </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="I71">
+        <f>+Table4[[#This Row],[Qty]]*8</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
-      <c r="G72" s="15"/>
-      <c r="H72" s="14">
+      <c r="D72" t="s">
+        <v>62</v>
+      </c>
+      <c r="E72" t="s">
+        <v>56</v>
+      </c>
+      <c r="F72">
+        <v>4</v>
+      </c>
+      <c r="G72" s="10">
+        <v>0.214</v>
+      </c>
+      <c r="H72" s="3">
+        <f>+F72*G72</f>
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="I72">
+        <f>+Table4[[#This Row],[Qty]]*8</f>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" t="s">
+        <v>63</v>
+      </c>
+      <c r="E73" t="s">
+        <v>56</v>
+      </c>
+      <c r="F73">
+        <v>2</v>
+      </c>
+      <c r="G73" s="10">
+        <v>0.214</v>
+      </c>
+      <c r="H73" s="3">
+        <f>+F73*G73</f>
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="I73">
+        <f>+Table4[[#This Row],[Qty]]*8</f>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="G74" s="15"/>
+      <c r="H74" s="14">
         <f>SUBTOTAL(109,Table4[Total Cost])</f>
-        <v>6.1630000000000003</v>
+        <v>7.7110000000000012</v>
       </c>
     </row>
   </sheetData>
@@ -2272,18 +2344,19 @@
     <hyperlink ref="C8" r:id="rId4" xr:uid="{8AFB8533-6E4E-46B4-B8D9-FFFE940BAA89}"/>
     <hyperlink ref="C7" r:id="rId5" display="Images SI - Uranium Ore" xr:uid="{2A42E8E4-BEF6-4EA2-A0A4-DCE432363EC4}"/>
     <hyperlink ref="C58" r:id="rId6" xr:uid="{DFB97EF8-2D11-41EA-93D2-F9D44BB1F7E8}"/>
-    <hyperlink ref="C59" r:id="rId7" xr:uid="{B558DB4E-2986-4C97-860B-41251108BACC}"/>
-    <hyperlink ref="C60" r:id="rId8" xr:uid="{CED55952-7AA0-43D2-AA98-56F5292C2EAC}"/>
-    <hyperlink ref="C61" r:id="rId9" xr:uid="{34EEC311-38EF-4430-9526-0F77F964AECA}"/>
-    <hyperlink ref="C62" r:id="rId10" xr:uid="{F6A0BDC3-0ED2-48CA-9FF7-7CC73CA1EA9E}"/>
+    <hyperlink ref="C60" r:id="rId7" xr:uid="{CED55952-7AA0-43D2-AA98-56F5292C2EAC}"/>
+    <hyperlink ref="C61" r:id="rId8" xr:uid="{34EEC311-38EF-4430-9526-0F77F964AECA}"/>
+    <hyperlink ref="C62" r:id="rId9" xr:uid="{F6A0BDC3-0ED2-48CA-9FF7-7CC73CA1EA9E}"/>
+    <hyperlink ref="C63" r:id="rId10" xr:uid="{D9B28C1C-D258-4CC2-8B8F-B0845496C76F}"/>
+    <hyperlink ref="C59" r:id="rId11" xr:uid="{872A5602-DD7F-4066-A3CA-EC11247F70A8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId11"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId12"/>
   <tableParts count="4">
-    <tablePart r:id="rId12"/>
     <tablePart r:id="rId13"/>
     <tablePart r:id="rId14"/>
     <tablePart r:id="rId15"/>
+    <tablePart r:id="rId16"/>
   </tableParts>
 </worksheet>
 </file>